--- a/config/frappe/imports/组织与岗位导入模板.xlsx
+++ b/config/frappe/imports/组织与岗位导入模板.xlsx
@@ -2,10 +2,10 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部门" sheetId="1" r:id="Rbfd65cd16b574fba"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岗位" sheetId="2" r:id="Re116d6e028a94664"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工任职" sheetId="3" r:id="Rce0e01a96eca4c26"/>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="4" r:id="R881592e1cbe74c80"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="部门" sheetId="1" r:id="Rd7ef0b1f82704fd7"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="岗位" sheetId="2" r:id="Ra750212bf701412f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="员工任职" sheetId="3" r:id="R28edcfe2ad1a4f0b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="说明" sheetId="4" r:id="R47b52b2b96844f3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -2329,16 +2329,16 @@
         <x:v>工作簿</x:v>
       </x:c>
       <x:c r="B4" s="14" t="str">
-        <x:v>格式</x:v>
+        <x:v>员工先建档</x:v>
       </x:c>
       <x:c r="C4" s="14" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D4" s="14" t="str">
-        <x:v>仅用 xlsx，单元格填写值，不使用公式、合并单元格或新增列。空行忽略，部分填写的行仍须校验。</x:v>
+        <x:v>HR 先在后台建立员工档案并填写真实的性别、出生日期和工号。本模板只按公司及工号更新既有员工任职信息，不新建员工；工号找不到或不唯一则整批拒绝。</x:v>
       </x:c>
       <x:c r="E4" s="14" t="str">
-        <x:v>第 1 行列名不改</x:v>
+        <x:v>不填写虚构性别或生日</x:v>
       </x:c>
     </x:row>
     <x:row r="5" ht="66" customHeight="1">
@@ -2346,33 +2346,33 @@
         <x:v>工作簿</x:v>
       </x:c>
       <x:c r="B5" s="14" t="str">
-        <x:v>敏感信息</x:v>
+        <x:v>格式</x:v>
       </x:c>
       <x:c r="C5" s="14" t="str">
-        <x:v>禁止</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D5" s="14" t="str">
-        <x:v>不得添加手机号、身份证号、银行卡或薪资列，也不把这些内容写进姓名、职责等其他单元格。由 HR 在后台录入。</x:v>
+        <x:v>仅用 xlsx，单元格填写值，不使用公式、合并单元格或新增列。空行忽略，部分填写的行仍须校验。</x:v>
       </x:c>
       <x:c r="E5" s="14" t="str">
-        <x:v>不经过此 Excel</x:v>
+        <x:v>第 1 行列名不改</x:v>
       </x:c>
     </x:row>
     <x:row r="6" ht="66" customHeight="1">
       <x:c r="A6" s="13" t="str">
-        <x:v>部门</x:v>
+        <x:v>工作簿</x:v>
       </x:c>
       <x:c r="B6" s="13" t="str">
-        <x:v>名称</x:v>
+        <x:v>敏感信息</x:v>
       </x:c>
       <x:c r="C6" s="13" t="str">
-        <x:v>是</x:v>
+        <x:v>禁止</x:v>
       </x:c>
       <x:c r="D6" s="13" t="str">
-        <x:v>同一文件内唯一，不能含英文逗号。已有部门使用完整名称（含公司缩写），新部门填写拟创建名称。</x:v>
+        <x:v>不得添加手机号、身份证号、银行卡或薪资列，也不把这些内容写进姓名、职责等其他单元格。由 HR 在后台录入。</x:v>
       </x:c>
       <x:c r="E6" s="13" t="str">
-        <x:v>示例人事部</x:v>
+        <x:v>不经过此 Excel</x:v>
       </x:c>
     </x:row>
     <x:row r="7" ht="66" customHeight="1">
@@ -2380,33 +2380,33 @@
         <x:v>部门</x:v>
       </x:c>
       <x:c r="B7" s="13" t="str">
-        <x:v>上级部门</x:v>
+        <x:v>名称</x:v>
       </x:c>
       <x:c r="C7" s="13" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D7" s="13" t="str">
-        <x:v>留空表示根部门。非空时引用本文件的部门名称或系统已有部门完整名称。不得指向自身或形成循环。</x:v>
+        <x:v>同一文件内唯一，不能含英文逗号。已有部门使用完整名称（含公司缩写），新部门填写拟创建名称。</x:v>
       </x:c>
       <x:c r="E7" s="13" t="str">
-        <x:v>示例总部</x:v>
+        <x:v>示例人事部</x:v>
       </x:c>
     </x:row>
     <x:row r="8" ht="66" customHeight="1">
       <x:c r="A8" s="13" t="str">
-        <x:v>岗位</x:v>
+        <x:v>部门</x:v>
       </x:c>
       <x:c r="B8" s="13" t="str">
-        <x:v>名称</x:v>
+        <x:v>上级部门</x:v>
       </x:c>
       <x:c r="C8" s="13" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="D8" s="13" t="str">
-        <x:v>同一文件内唯一，不能含英文逗号。引用已有岗位时使用完整名称；重复导入按同名记录更新，不另建副本。</x:v>
+        <x:v>留空表示根部门。非空时引用本文件的部门名称或系统已有部门完整名称。不得指向自身或形成循环。</x:v>
       </x:c>
       <x:c r="E8" s="13" t="str">
-        <x:v>示例HR专员</x:v>
+        <x:v>示例总部</x:v>
       </x:c>
     </x:row>
     <x:row r="9" ht="66" customHeight="1">
@@ -2414,17 +2414,16 @@
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="B9" s="13" t="str">
-        <x:v>岗位职责</x:v>
+        <x:v>名称</x:v>
       </x:c>
       <x:c r="C9" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D9" s="13" t="str">
-        <x:v>使用多行纯文本，Excel 中可用 Alt+Enter 换行。后续导入转为段落或列表，写入岗位职责字段。不要填 HTML 或敏感信息。</x:v>
+        <x:v>同一文件内唯一，不能含英文逗号。引用已有岗位时使用完整名称；重复导入按同名记录更新，不另建副本。</x:v>
       </x:c>
       <x:c r="E9" s="13" t="str">
-        <x:v>维护组织资料
-办理入离职手续</x:v>
+        <x:v>示例HR专员</x:v>
       </x:c>
     </x:row>
     <x:row r="10" ht="66" customHeight="1">
@@ -2432,16 +2431,17 @@
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="B10" s="13" t="str">
-        <x:v>可见的知识空间</x:v>
+        <x:v>岗位职责</x:v>
       </x:c>
       <x:c r="C10" s="13" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D10" s="13" t="str">
-        <x:v>填写已有“知识空间”的完整名称，多个用英文逗号分隔，不填 Wiki Space 名称或 Dify 知识库 ID。空间名称本身不能含英文逗号。</x:v>
+        <x:v>使用多行纯文本，Excel 中可用 Alt+Enter 换行。后续导入转为段落或列表，写入岗位职责字段。不要填 HTML 或敏感信息。</x:v>
       </x:c>
       <x:c r="E10" s="13" t="str">
-        <x:v>公司制度,人事手册</x:v>
+        <x:v>维护组织资料
+办理入离职手续</x:v>
       </x:c>
     </x:row>
     <x:row r="11" ht="66" customHeight="1">
@@ -2449,33 +2449,33 @@
         <x:v>岗位</x:v>
       </x:c>
       <x:c r="B11" s="13" t="str">
-        <x:v>知识空间留空</x:v>
+        <x:v>可见的知识空间</x:v>
       </x:c>
       <x:c r="C11" s="13" t="str">
         <x:v>否</x:v>
       </x:c>
       <x:c r="D11" s="13" t="str">
-        <x:v>留空表示该岗位不指定额外知识空间，不代表全员可见。全员可见、部门可见由知识空间配置决定。</x:v>
+        <x:v>填写已有“知识空间”的完整名称，多个用英文逗号分隔，不填 Wiki Space 名称或 Dify 知识库 ID。空间名称本身不能含英文逗号。</x:v>
       </x:c>
       <x:c r="E11" s="13" t="str">
-        <x:v>示例岗位均留空</x:v>
+        <x:v>公司制度,人事手册</x:v>
       </x:c>
     </x:row>
     <x:row r="12" ht="66" customHeight="1">
       <x:c r="A12" s="13" t="str">
-        <x:v>员工任职</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="B12" s="13" t="str">
-        <x:v>工号</x:v>
+        <x:v>知识空间留空</x:v>
       </x:c>
       <x:c r="C12" s="13" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="D12" s="13" t="str">
-        <x:v>文本格式，同公司唯一，不能重复。不要改成数字列，以免丢失前导零；重复导入用工号定位已有员工。</x:v>
+        <x:v>留空表示该岗位不指定额外知识空间，不代表全员可见。全员可见、部门可见由知识空间配置决定。</x:v>
       </x:c>
       <x:c r="E12" s="13" t="str">
-        <x:v>DEMO0001</x:v>
+        <x:v>示例岗位均留空</x:v>
       </x:c>
     </x:row>
     <x:row r="13" ht="66" customHeight="1">
@@ -2483,16 +2483,16 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B13" s="13" t="str">
-        <x:v>姓名</x:v>
+        <x:v>工号</x:v>
       </x:c>
       <x:c r="C13" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D13" s="13" t="str">
-        <x:v>填写姓名，不在姓名中附加电话、身份证等信息。不同员工可同名，使用工号区分。</x:v>
+        <x:v>文本格式，同公司唯一，不能重复。不要改成数字列，以免丢失前导零；重复导入用工号定位已有员工。</x:v>
       </x:c>
       <x:c r="E13" s="13" t="str">
-        <x:v>示例甲</x:v>
+        <x:v>DEMO0001</x:v>
       </x:c>
     </x:row>
     <x:row r="14" ht="66" customHeight="1">
@@ -2500,16 +2500,16 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B14" s="13" t="str">
-        <x:v>企业微信 userid</x:v>
+        <x:v>姓名</x:v>
       </x:c>
       <x:c r="C14" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D14" s="13" t="str">
-        <x:v>文本格式，使用企业微信通讯录的 userid 原值，区分大小写；全文件及系统内不得与其他员工重复。不得使用手机号或昵称代替。</x:v>
+        <x:v>填写姓名，不在姓名中附加电话、身份证等信息。不同员工可同名，使用工号区分。</x:v>
       </x:c>
       <x:c r="E14" s="13" t="str">
-        <x:v>demo_manager_01</x:v>
+        <x:v>示例甲</x:v>
       </x:c>
     </x:row>
     <x:row r="15" ht="66" customHeight="1">
@@ -2517,16 +2517,16 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B15" s="13" t="str">
-        <x:v>部门</x:v>
+        <x:v>企业微信 userid</x:v>
       </x:c>
       <x:c r="C15" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D15" s="13" t="str">
-        <x:v>引用本文件部门名称或系统已有部门完整名称。不能用部门简称猜测匹配。</x:v>
+        <x:v>文本格式，使用企业微信通讯录的 userid 原值，区分大小写；全文件及系统内不得与其他员工重复。不得使用手机号或昵称代替。</x:v>
       </x:c>
       <x:c r="E15" s="13" t="str">
-        <x:v>示例总部</x:v>
+        <x:v>demo_manager_01</x:v>
       </x:c>
     </x:row>
     <x:row r="16" ht="66" customHeight="1">
@@ -2534,16 +2534,16 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B16" s="13" t="str">
-        <x:v>岗位</x:v>
+        <x:v>部门</x:v>
       </x:c>
       <x:c r="C16" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D16" s="13" t="str">
-        <x:v>引用本文件岗位名称或系统已有岗位完整名称，不得填写不存在的岗位。</x:v>
+        <x:v>引用本文件部门名称或系统已有部门完整名称。不能用部门简称猜测匹配。</x:v>
       </x:c>
       <x:c r="E16" s="13" t="str">
-        <x:v>示例负责人</x:v>
+        <x:v>示例总部</x:v>
       </x:c>
     </x:row>
     <x:row r="17" ht="66" customHeight="1">
@@ -2551,16 +2551,16 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B17" s="13" t="str">
-        <x:v>直属上级工号</x:v>
+        <x:v>岗位</x:v>
       </x:c>
       <x:c r="C17" s="13" t="str">
-        <x:v>否</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D17" s="13" t="str">
-        <x:v>引用同公司系统已有员工工号或本文件工号。最高负责人可留空；不得指向本人或形成循环。</x:v>
+        <x:v>引用本文件岗位名称或系统已有岗位完整名称，不得填写不存在的岗位。</x:v>
       </x:c>
       <x:c r="E17" s="13" t="str">
-        <x:v>DEMO0001</x:v>
+        <x:v>示例负责人</x:v>
       </x:c>
     </x:row>
     <x:row r="18" ht="66" customHeight="1">
@@ -2568,50 +2568,50 @@
         <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B18" s="13" t="str">
-        <x:v>入职日期</x:v>
+        <x:v>直属上级工号</x:v>
       </x:c>
       <x:c r="C18" s="13" t="str">
-        <x:v>是</x:v>
+        <x:v>否</x:v>
       </x:c>
       <x:c r="D18" s="13" t="str">
-        <x:v>填写 Excel 日期，显示为 yyyy-mm-dd，使用四位年份。不要填“今天”等描述。</x:v>
+        <x:v>引用同公司系统已有员工工号或本文件工号。最高负责人可留空；不得指向本人或形成循环。</x:v>
       </x:c>
       <x:c r="E18" s="13" t="str">
-        <x:v>2026-10-01</x:v>
+        <x:v>DEMO0001</x:v>
       </x:c>
     </x:row>
     <x:row r="19" ht="66" customHeight="1">
       <x:c r="A19" s="13" t="str">
-        <x:v>说明</x:v>
+        <x:v>员工任职</x:v>
       </x:c>
       <x:c r="B19" s="13" t="str">
-        <x:v>本表</x:v>
+        <x:v>入职日期</x:v>
       </x:c>
       <x:c r="C19" s="13" t="str">
-        <x:v>不导入</x:v>
+        <x:v>是</x:v>
       </x:c>
       <x:c r="D19" s="13" t="str">
-        <x:v>本表只说明规则，不作为部门、岗位或员工数据导入。所有示例都是合成数据。</x:v>
+        <x:v>填写 Excel 日期，显示为 yyyy-mm-dd，使用四位年份。不要填“今天”等描述。</x:v>
       </x:c>
       <x:c r="E19" s="13" t="str">
-        <x:v>不包含真实员工</x:v>
+        <x:v>2026-10-01</x:v>
       </x:c>
     </x:row>
     <x:row r="20" ht="66" customHeight="1">
       <x:c r="A20" s="13" t="str">
-        <x:v>导入行为</x:v>
+        <x:v>说明</x:v>
       </x:c>
       <x:c r="B20" s="13" t="str">
-        <x:v>权限</x:v>
+        <x:v>本表</x:v>
       </x:c>
       <x:c r="C20" s="13" t="str">
-        <x:v>限定</x:v>
+        <x:v>不导入</x:v>
       </x:c>
       <x:c r="D20" s="13" t="str">
-        <x:v>后续导入功能仅供 HR Manager 或 System Manager 使用。Excel 文件不能授予用户角色或改变审批权限。</x:v>
+        <x:v>本表只说明规则，不作为部门、岗位或员工数据导入。所有示例都是合成数据。</x:v>
       </x:c>
       <x:c r="E20" s="13" t="str">
-        <x:v>普通员工不可导入</x:v>
+        <x:v>不包含真实员工</x:v>
       </x:c>
     </x:row>
     <x:row r="21" ht="66" customHeight="1">
@@ -2619,16 +2619,16 @@
         <x:v>导入行为</x:v>
       </x:c>
       <x:c r="B21" s="13" t="str">
-        <x:v>校验与保存</x:v>
+        <x:v>权限</x:v>
       </x:c>
       <x:c r="C21" s="13" t="str">
-        <x:v>是</x:v>
+        <x:v>限定</x:v>
       </x:c>
       <x:c r="D21" s="13" t="str">
-        <x:v>后续功能先校验全文件，逐项列出工作表、行号、列名和错误；有错则一行不导，全部通过后在一个事务中保存。</x:v>
+        <x:v>后续导入功能仅供 HR Manager 或 System Manager 使用。Excel 文件不能授予用户角色或改变审批权限。</x:v>
       </x:c>
       <x:c r="E21" s="13" t="str">
-        <x:v>先修正错误再导入</x:v>
+        <x:v>普通员工不可导入</x:v>
       </x:c>
     </x:row>
     <x:row r="22" ht="66" customHeight="1">
@@ -2636,47 +2636,64 @@
         <x:v>导入行为</x:v>
       </x:c>
       <x:c r="B22" s="13" t="str">
-        <x:v>更新与审批人</x:v>
+        <x:v>校验与保存</x:v>
       </x:c>
       <x:c r="C22" s="13" t="str">
         <x:v>是</x:v>
       </x:c>
       <x:c r="D22" s="13" t="str">
-        <x:v>部门按公司及名称、岗位按系统名称、员工按公司及工号更新。直属上级写入 reports_to；请假审批人另按 P2-G1 规则配置，不在本表指定。</x:v>
+        <x:v>后续功能先校验全文件，逐项列出工作表、行号、列名和错误；有错则一行不导，全部通过后在一个事务中保存。</x:v>
       </x:c>
       <x:c r="E22" s="13" t="str">
-        <x:v>重复导入不重复建</x:v>
+        <x:v>先修正错误再导入</x:v>
       </x:c>
     </x:row>
     <x:row r="23" ht="66" customHeight="1">
       <x:c r="A23" s="13" t="str">
+        <x:v>导入行为</x:v>
+      </x:c>
+      <x:c r="B23" s="13" t="str">
+        <x:v>更新与审批人</x:v>
+      </x:c>
+      <x:c r="C23" s="13" t="str">
+        <x:v>是</x:v>
+      </x:c>
+      <x:c r="D23" s="13" t="str">
+        <x:v>部门按公司及名称、岗位按系统名称、员工按公司及工号更新。直属上级写入 reports_to；请假审批人另按 P2-G1 规则配置，不在本表指定。</x:v>
+      </x:c>
+      <x:c r="E23" s="13" t="str">
+        <x:v>重复导入不重复建</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" ht="66" customHeight="1">
+      <x:c r="A24" s="13" t="str">
         <x:v>版本</x:v>
       </x:c>
-      <x:c r="B23" s="13" t="str">
+      <x:c r="B24" s="13" t="str">
         <x:v>交付范围</x:v>
       </x:c>
-      <x:c r="C23" s="13" t="str">
+      <x:c r="C24" s="13" t="str">
         <x:v>模板</x:v>
       </x:c>
-      <x:c r="D23" s="13" t="str">
+      <x:c r="D24" s="13" t="str">
         <x:v>本次先交付模板。Frappe 后台导入功能尚未交付，不能直接上传到原生 Data Import 当成已可导入。</x:v>
       </x:c>
-      <x:c r="E23" s="13" t="str">
+      <x:c r="E24" s="13" t="str">
         <x:v>模板格式版本 1</x:v>
       </x:c>
     </x:row>
-    <x:row r="24" ht="100" customHeight="1">
-      <x:c r="A24" s="13" t="str">
+    <x:row r="25" ht="100" customHeight="1">
+      <x:c r="A25" s="13" t="str">
         <x:v>依据</x:v>
       </x:c>
-      <x:c r="B24" s="13" t="str">
+      <x:c r="B25" s="13" t="str">
         <x:v>任务卡</x:v>
       </x:c>
-      <x:c r="C24" s="13" t="str"/>
-      <x:c r="D24" s="13" t="str">
+      <x:c r="C25" s="13" t="str"/>
+      <x:c r="D25" s="13" t="str">
         <x:v>P1-G2：组织和岗位职责的 Excel 模板与导入。</x:v>
       </x:c>
-      <x:c r="E24" s="13" t="str">
+      <x:c r="E25" s="13" t="str">
         <x:v>https://github.com/qianjie0720-sys/enterprise-base/blob/755926f469868b8521aa263a14515717d61d9c54/docs/task-cards/P1-G2-Excel模板与导入.md</x:v>
       </x:c>
     </x:row>
